--- a/artfynd/A 1630-2024 artfynd.xlsx
+++ b/artfynd/A 1630-2024 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 1630-2024 artfynd.xlsx
+++ b/artfynd/A 1630-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY23"/>
+  <dimension ref="A1:AY24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,51 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>114531009</v>
+        <v>114531021</v>
       </c>
       <c r="B2" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92348</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>5420</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -727,10 +721,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>442391</v>
+        <v>442594</v>
       </c>
       <c r="R2" t="n">
-        <v>6485756</v>
+        <v>6485528</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -763,6 +757,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-02-03</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>En gammal fruktkropp</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -789,51 +788,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>114531001</v>
+        <v>114531040</v>
       </c>
       <c r="B3" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>5966</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -841,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>442588</v>
+        <v>442461</v>
       </c>
       <c r="R3" t="n">
-        <v>6485522</v>
+        <v>6485642</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -879,6 +872,11 @@
           <t>2024-02-03</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>3 gamla fruktkroppar</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -896,58 +894,49 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Jon Liljebäck, Rolf-Göran Carlsson, Ove Grönlund, Liselotte Larsson , Kurt-Anders Johansson, Hanna Liljebäck, Ada  Arenander</t>
+          <t>Jon Liljebäck, Ada  Arenander, Hanna Liljebäck, Kurt-Anders Johansson, Liselotte Larsson , Ove Grönlund, Rolf-Göran Carlsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>114531016</v>
+        <v>114531070</v>
       </c>
       <c r="B4" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58112</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>103020</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -955,13 +944,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>442458</v>
+        <v>442428</v>
       </c>
       <c r="R4" t="n">
-        <v>6485643</v>
+        <v>6485712</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1010,22 +999,17 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Jon Liljebäck, Rolf-Göran Carlsson, Ove Grönlund, Liselotte Larsson , Kurt-Anders Johansson, Hanna Liljebäck, Ada  Arenander</t>
+          <t>Jon Liljebäck, Ada  Arenander, Hanna Liljebäck, Kurt-Anders Johansson, Liselotte Larsson , Ove Grönlund, Rolf-Göran Carlsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>114531005</v>
+        <v>114530999</v>
       </c>
       <c r="B5" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1052,7 +1036,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>39</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1069,10 +1053,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>442584</v>
+        <v>442575</v>
       </c>
       <c r="R5" t="n">
-        <v>6485677</v>
+        <v>6485511</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1107,12 +1091,18 @@
           <t>2024-02-03</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Samlade i en fin tuva</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1124,22 +1114,17 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Jon Liljebäck, Rolf-Göran Carlsson, Ove Grönlund, Liselotte Larsson , Kurt-Anders Johansson, Hanna Liljebäck, Ada  Arenander</t>
+          <t>Jon Liljebäck, Ada  Arenander, Hanna Liljebäck, Kurt-Anders Johansson, Liselotte Larsson , Ove Grönlund, Rolf-Göran Carlsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>114530999</v>
+        <v>114531001</v>
       </c>
       <c r="B6" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1166,7 +1151,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1183,10 +1168,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>442575</v>
+        <v>442588</v>
       </c>
       <c r="R6" t="n">
-        <v>6485511</v>
+        <v>6485522</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1221,18 +1206,12 @@
           <t>2024-02-03</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Samlade i en fin tuva</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1244,22 +1223,17 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Jon Liljebäck, Ada  Arenander, Hanna Liljebäck, Kurt-Anders Johansson, Liselotte Larsson , Ove Grönlund, Rolf-Göran Carlsson</t>
+          <t>Jon Liljebäck, Rolf-Göran Carlsson, Ove Grönlund, Liselotte Larsson , Kurt-Anders Johansson, Hanna Liljebäck, Ada  Arenander</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>114531011</v>
+        <v>114531004</v>
       </c>
       <c r="B7" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1286,7 +1260,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1303,10 +1277,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>442346</v>
+        <v>442570</v>
       </c>
       <c r="R7" t="n">
-        <v>6485782</v>
+        <v>6485544</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1365,15 +1339,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>114531007</v>
+        <v>114531005</v>
       </c>
       <c r="B8" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1400,7 +1369,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1417,10 +1386,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>442535</v>
+        <v>442584</v>
       </c>
       <c r="R8" t="n">
-        <v>6485697</v>
+        <v>6485677</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1479,15 +1448,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>114531010</v>
+        <v>114531006</v>
       </c>
       <c r="B9" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1514,7 +1478,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1531,10 +1495,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>442387</v>
+        <v>442556</v>
       </c>
       <c r="R9" t="n">
-        <v>6485766</v>
+        <v>6485675</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1593,15 +1557,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>114531053</v>
+        <v>114531007</v>
       </c>
       <c r="B10" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1628,7 +1587,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>26</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1645,10 +1604,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>442375</v>
+        <v>442535</v>
       </c>
       <c r="R10" t="n">
-        <v>6485762</v>
+        <v>6485697</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1700,22 +1659,17 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Jon Liljebäck, Ada  Arenander, Hanna Liljebäck, Kurt-Anders Johansson, Liselotte Larsson , Ove Grönlund, Rolf-Göran Carlsson</t>
+          <t>Jon Liljebäck, Rolf-Göran Carlsson, Ove Grönlund, Liselotte Larsson , Kurt-Anders Johansson, Hanna Liljebäck, Ada  Arenander</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>114531012</v>
+        <v>114531008</v>
       </c>
       <c r="B11" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1742,7 +1696,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1759,10 +1713,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>442363</v>
+        <v>442511</v>
       </c>
       <c r="R11" t="n">
-        <v>6485767</v>
+        <v>6485705</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1821,15 +1775,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>114531008</v>
+        <v>114531009</v>
       </c>
       <c r="B12" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1856,7 +1805,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>43</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1873,10 +1822,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>442511</v>
+        <v>442391</v>
       </c>
       <c r="R12" t="n">
-        <v>6485705</v>
+        <v>6485756</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1935,15 +1884,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>114531052</v>
+        <v>114531010</v>
       </c>
       <c r="B13" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1970,7 +1914,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1987,10 +1931,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>442347</v>
+        <v>442387</v>
       </c>
       <c r="R13" t="n">
-        <v>6485768</v>
+        <v>6485766</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -2042,57 +1986,53 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Jon Liljebäck, Ada  Arenander, Hanna Liljebäck, Kurt-Anders Johansson, Liselotte Larsson , Ove Grönlund, Rolf-Göran Carlsson</t>
+          <t>Jon Liljebäck, Rolf-Göran Carlsson, Ove Grönlund, Liselotte Larsson , Kurt-Anders Johansson, Hanna Liljebäck, Ada  Arenander</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>114531021</v>
+        <v>114531011</v>
       </c>
       <c r="B14" t="n">
-        <v>90735</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5420</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2100,10 +2040,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>442594</v>
+        <v>442346</v>
       </c>
       <c r="R14" t="n">
-        <v>6485528</v>
+        <v>6485782</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2136,11 +2076,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-02-03</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>En gammal fruktkropp</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2167,15 +2102,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>114531061</v>
+        <v>114531012</v>
       </c>
       <c r="B15" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2202,7 +2132,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2219,10 +2149,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>442550</v>
+        <v>442363</v>
       </c>
       <c r="R15" t="n">
-        <v>6485570</v>
+        <v>6485767</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2274,54 +2204,53 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Jon Liljebäck, Ada  Arenander, Hanna Liljebäck, Kurt-Anders Johansson, Liselotte Larsson , Ove Grönlund, Rolf-Göran Carlsson</t>
+          <t>Jon Liljebäck, Rolf-Göran Carlsson, Ove Grönlund, Liselotte Larsson , Kurt-Anders Johansson, Hanna Liljebäck, Ada  Arenander</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>114531070</v>
+        <v>114531014</v>
       </c>
       <c r="B16" t="n">
-        <v>57412</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103020</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2329,13 +2258,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>442428</v>
+        <v>442348</v>
       </c>
       <c r="R16" t="n">
-        <v>6485712</v>
+        <v>6485776</v>
       </c>
       <c r="S16" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2384,22 +2313,17 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Jon Liljebäck, Ada  Arenander, Hanna Liljebäck, Kurt-Anders Johansson, Liselotte Larsson , Ove Grönlund, Rolf-Göran Carlsson</t>
+          <t>Jon Liljebäck, Rolf-Göran Carlsson, Ove Grönlund, Liselotte Larsson , Kurt-Anders Johansson, Hanna Liljebäck, Ada  Arenander</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>114531056</v>
+        <v>114531016</v>
       </c>
       <c r="B17" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2443,10 +2367,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>442390</v>
+        <v>442458</v>
       </c>
       <c r="R17" t="n">
-        <v>6485773</v>
+        <v>6485643</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2498,22 +2422,17 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Jon Liljebäck, Ada  Arenander, Hanna Liljebäck, Kurt-Anders Johansson, Liselotte Larsson , Ove Grönlund, Rolf-Göran Carlsson</t>
+          <t>Jon Liljebäck, Rolf-Göran Carlsson, Ove Grönlund, Liselotte Larsson , Kurt-Anders Johansson, Hanna Liljebäck, Ada  Arenander</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>114531014</v>
+        <v>114531052</v>
       </c>
       <c r="B18" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2540,7 +2459,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>23</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2557,10 +2476,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>442348</v>
+        <v>442347</v>
       </c>
       <c r="R18" t="n">
-        <v>6485776</v>
+        <v>6485768</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2612,22 +2531,17 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Jon Liljebäck, Rolf-Göran Carlsson, Ove Grönlund, Liselotte Larsson , Kurt-Anders Johansson, Hanna Liljebäck, Ada  Arenander</t>
+          <t>Jon Liljebäck, Ada  Arenander, Hanna Liljebäck, Kurt-Anders Johansson, Liselotte Larsson , Ove Grönlund, Rolf-Göran Carlsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>114531006</v>
+        <v>114531053</v>
       </c>
       <c r="B19" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2654,7 +2568,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2671,10 +2585,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>442556</v>
+        <v>442375</v>
       </c>
       <c r="R19" t="n">
-        <v>6485675</v>
+        <v>6485762</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2726,22 +2640,17 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Jon Liljebäck, Rolf-Göran Carlsson, Ove Grönlund, Liselotte Larsson , Kurt-Anders Johansson, Hanna Liljebäck, Ada  Arenander</t>
+          <t>Jon Liljebäck, Ada  Arenander, Hanna Liljebäck, Kurt-Anders Johansson, Liselotte Larsson , Ove Grönlund, Rolf-Göran Carlsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>114531058</v>
+        <v>114531055</v>
       </c>
       <c r="B20" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2768,7 +2677,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2785,10 +2694,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>442338</v>
+        <v>442362</v>
       </c>
       <c r="R20" t="n">
-        <v>6485762</v>
+        <v>6485788</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2847,15 +2756,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>114531004</v>
+        <v>114531056</v>
       </c>
       <c r="B21" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2882,7 +2786,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2899,10 +2803,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>442570</v>
+        <v>442390</v>
       </c>
       <c r="R21" t="n">
-        <v>6485544</v>
+        <v>6485773</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2954,22 +2858,17 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Jon Liljebäck, Rolf-Göran Carlsson, Ove Grönlund, Liselotte Larsson , Kurt-Anders Johansson, Hanna Liljebäck, Ada  Arenander</t>
+          <t>Jon Liljebäck, Ada  Arenander, Hanna Liljebäck, Kurt-Anders Johansson, Liselotte Larsson , Ove Grönlund, Rolf-Göran Carlsson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>114531055</v>
+        <v>114531058</v>
       </c>
       <c r="B22" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2996,7 +2895,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -3013,10 +2912,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>442362</v>
+        <v>442338</v>
       </c>
       <c r="R22" t="n">
-        <v>6485788</v>
+        <v>6485762</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -3075,50 +2974,38 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>114531040</v>
+        <v>114531060</v>
       </c>
       <c r="B23" t="n">
-        <v>91628</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5966</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3126,10 +3013,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>442461</v>
+        <v>442321</v>
       </c>
       <c r="R23" t="n">
-        <v>6485642</v>
+        <v>6485795</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3164,11 +3051,6 @@
           <t>2024-02-03</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>3 gamla fruktkroppar</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -3190,6 +3072,115 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>114531061</v>
+      </c>
+      <c r="B24" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Lilla Väring 3:18, Vg</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>442550</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6485570</v>
+      </c>
+      <c r="S24" t="n">
+        <v>15</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Skövde</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Väring</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2024-02-03</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2024-02-03</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Jon Liljebäck</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Jon Liljebäck, Ada  Arenander, Hanna Liljebäck, Kurt-Anders Johansson, Liselotte Larsson , Ove Grönlund, Rolf-Göran Carlsson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 1630-2024 artfynd.xlsx
+++ b/artfynd/A 1630-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY24"/>
+  <dimension ref="A1:AZ24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -785,6 +790,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114531021</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -898,6 +908,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114531040</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1003,6 +1018,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114531070</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1118,6 +1138,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114530999</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1227,6 +1252,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114531001</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1336,6 +1366,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114531004</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1445,6 +1480,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114531005</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1554,6 +1594,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114531006</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1663,6 +1708,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114531007</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1772,6 +1822,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114531008</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1881,6 +1936,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114531009</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1990,6 +2050,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114531010</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2099,6 +2164,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114531011</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2208,6 +2278,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114531012</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2317,6 +2392,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114531014</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2426,6 +2506,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114531016</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2535,6 +2620,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114531052</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2644,6 +2734,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114531053</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2753,6 +2848,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114531055</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2862,6 +2962,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114531056</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2971,6 +3076,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114531058</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3072,6 +3182,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114531060</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3181,8 +3296,38 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114531061</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>